--- a/data/gravel/Tumbleweed Stargazer Ti 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BD7E38B-F2C4-8F4C-9EBD-23F6463D6AE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCF60F1-27F8-A04B-B4D3-4629E9A2BBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1160" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="103">
   <si>
     <t>brand</t>
   </si>
@@ -339,6 +339,9 @@
   </si>
   <si>
     <t>Stargazer Ti</t>
+  </si>
+  <si>
+    <t>https://tumbleweed.cc/cdn/shop/files/Awards_lockups_1.png?v=1758651916&amp;width=1000</t>
   </si>
 </sst>
 </file>
@@ -724,6 +727,11 @@
         <v>99</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>102</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Tumbleweed Stargazer Ti 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FCF60F1-27F8-A04B-B4D3-4629E9A2BBE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CA4596-B0B3-4D4C-A125-C801641E1174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1160" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="103">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
   <si>
     <t>brand</t>
   </si>
@@ -320,9 +320,6 @@
     <t>no</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Frame Geometry</t>
   </si>
   <si>
@@ -342,6 +339,15 @@
   </si>
   <si>
     <t>https://tumbleweed.cc/cdn/shop/files/Awards_lockups_1.png?v=1758651916&amp;width=1000</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Garden City, Idaho, USA</t>
+  </si>
+  <si>
+    <t>USD</t>
   </si>
 </sst>
 </file>
@@ -681,7 +687,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -700,7 +706,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
@@ -724,12 +730,12 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -745,7 +751,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
@@ -929,7 +935,7 @@
         <v>29</v>
       </c>
       <c r="B16" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C16">
         <v>63.5</v>
@@ -998,7 +1004,7 @@
         <v>34</v>
       </c>
       <c r="B19" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C19">
         <v>750</v>
@@ -1201,7 +1207,7 @@
         <v>50</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.3">
@@ -1423,7 +1429,15 @@
         <v>84</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>95</v>
+        <v>104</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Tumbleweed Stargazer Ti 2025.xlsx
+++ b/data/gravel/Tumbleweed Stargazer Ti 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CA4596-B0B3-4D4C-A125-C801641E1174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D554C6-47F7-AD48-96EC-1C4694363469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2900" yWindow="1160" windowWidth="25900" windowHeight="14700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -348,6 +348,24 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -687,7 +705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1275,168 +1293,198 @@
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>61</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>92</v>
+        <v>105</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>63</v>
-      </c>
-      <c r="B49">
-        <v>27.2</v>
+        <v>107</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>64</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>65</v>
-      </c>
-      <c r="B51">
-        <v>38</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>67</v>
-      </c>
-      <c r="B53">
-        <v>180</v>
+        <v>61</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>68</v>
-      </c>
-      <c r="B54">
-        <v>180</v>
+        <v>62</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>69</v>
+        <v>63</v>
+      </c>
+      <c r="B55">
+        <v>27.2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>71</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>93</v>
+        <v>65</v>
+      </c>
+      <c r="B57">
+        <v>38</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>73</v>
+        <v>67</v>
+      </c>
+      <c r="B59">
+        <v>180</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="B60">
-        <v>3</v>
+        <v>180</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>77</v>
+        <v>71</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>93</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>78</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>79</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>80</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>91</v>
+        <v>74</v>
+      </c>
+      <c r="B66">
+        <v>3</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>81</v>
-      </c>
-      <c r="B67">
-        <v>2850</v>
+        <v>75</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
+        <v>78</v>
+      </c>
+      <c r="B70" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>79</v>
+      </c>
+      <c r="B71" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>80</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>81</v>
+      </c>
+      <c r="B73">
+        <v>2850</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
         <v>84</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B76" s="1" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A71" s="1" t="s">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B77" s="1" t="s">
         <v>103</v>
       </c>
     </row>
